--- a/instrument/wiring_table.xlsx
+++ b/instrument/wiring_table.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R8b00f1323cdf4c8b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re0c112d4832644f7"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -28,403 +28,343 @@
     <x:t xml:space="preserve">Split</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Highland Technologies T660-2 Digital Delay Generator (Master)</x:t>
+    <x:t xml:space="preserve">Surelite YAG Nd:YAG Laser</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">No</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Fixed Sync OUT</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Output</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">DIO 16</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">HF2LI</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Back BNC</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Variable Sync OUT</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">DIO 17</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Flashlamp Sync OUT</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">DIO 18</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Daylight MIRcat QCL </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">TRIG IN</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Input</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">CH B</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">TRIG OUT</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">DIO 19</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">DB9 1 - Scan Direction</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">DIO 20</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">DB9 3 - Wavelength Trigger</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">DIO 22</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">DB9 4 - Process Trigger</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">CH C</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Back Terminal</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">DB9 5 - Reserved (Laser Output On/Off)</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">DISCONNECTED</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">DB9 6 - Interlock</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">UNUSED</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">DB9 7 - Ground</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Ground Bus</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">DB9 8 - Remote ON/OFF</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">DB9 9 - Ground</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Zurich Instruments HF2LI Lock-In Amplifier</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Clock</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Output</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">T660-1; HF2LI</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">No</x:t>
+    <x:t xml:space="preserve">T660-2</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Sample Detector</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Reference Detector</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">DIO 0 (Ext Ref)</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">CH A</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">DIO 0 (Ext Ref)</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">HF2LI</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">CH B</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">TRIG IN</x:t>
+    <x:t xml:space="preserve">DIO 2-8</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">YAG</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">MIRcat</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">CH C</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">DIO 1 (DAQ Trigger)</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">CH D</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">TRIG IN </x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">T660-1</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Highland Technologies T660-1 Digital Delay Generator (Slave)</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Input</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">T660-2</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">RS232 7 - Fire Command</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">YAG</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">RS232 6 - Q-Switch Command</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">DB9 4</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Back BNC</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">DISCONNECTED</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Surelite YAG Nd:YAG Laser</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Fixed Sync OUT</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">DIO 16</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Variable Sync OUT</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">DIO 17</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Flashlamp Sync OUT</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">DIO 18</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Daylight MIRcat QCL </x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">TRIG OUT</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">DIO 19</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">DB9 1 - Scan Direction</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">DIO 20</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">DB9 2 - Tuned / Scan Firing </x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">DIO 21</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">DB9 3 - Wavelength Trigger</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">DIO 22</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">DB9 4 - Process Trigger</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Back Terminal</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">DB9 5 - Reserved (Laser Output On/Off)</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">DB9 6 - Interlock</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">UNUSED</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">DB9 7 - Ground</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Ground Bus</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">DB9 8 - Remote ON/OFF</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">DB9 9 - Ground</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Zurich Instruments HF2LI Lock-In Amplifier</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Sample Detector</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Reference Detector</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">DIO 2-8</x:t>
+    <x:t xml:space="preserve">DIO 23-31</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">GND</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">AUX 1 (X/R 1)</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">C0</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">AUX 2 (Y/Theta 1)</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">C1</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">AUX 3 (X/R 2)</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">C2</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">AUX 4 (Y/Theta 2)</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">C3</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">PicoScope 5244D</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Front BNC</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">VCC</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">5V+</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Arduino</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">SIG</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">EN</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">D2</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">S0</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">D6</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">S1</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">D7</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">S2</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">D8</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">S3</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">D9</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">DIO 9</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">DIO 16 / C0</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">HF2LI / DMB 1-3</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">DIO 10</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">DIO 17 / C1</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">DIO 11</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">DIO 18 / C2</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">DIO 12</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">DIO 19 / C3</x:t>
+    <x:t xml:space="preserve">C4</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">DIO 13</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">DIO 20 / C4</x:t>
+    <x:t xml:space="preserve">C5</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">DIO 14</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">DIO 21 / C5</x:t>
+    <x:t xml:space="preserve">C6</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">DIO 15</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">DIO 22 / C6</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">DIO 23-31</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">GND</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">AUX 1 (X/R 1)</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">C0</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">AMB1-2</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">AUX 2 (Y/Theta 1)</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">C1</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">AUX 3 (X/R 2)</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">C2</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">AUX 4 (Y/Theta 2)</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">C3</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">PicoScope 5244D</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Front BNC</x:t>
+    <x:t xml:space="preserve">C7-15</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">D3</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">D10</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">D11</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">D12</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">D13</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">SPARE</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">A0</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">A1</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">A2</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">A3</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">A4</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Front Terminal</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">D4</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">AUX 1</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">AUX 2</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">AUX 3</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">AUX 4</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">C4-15</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Inpu</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Front - Terminal</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">D5</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Arduino UNO R4 Minima</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">5V</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">DMB1-3; AMB1-2</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">D0</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">D1</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">DMB1</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">DMB2</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">AMB1</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">AMB2</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">DMB1; AMB1</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">DMB2; AMB2</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">DMB3</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">VCC</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">5V+</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Arduino</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">SIG</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">EN</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">D2</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">S0</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">D6</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">S1</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">D7</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">S2</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">D8</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">S3</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">D9</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">C4</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">C5</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">C6</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">C7-15</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">D3</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">D10</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">D11</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">D12</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">D13</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">SPARE</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">A0</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">A1</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">A2</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">A3</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">A4</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Front Terminal</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">D4</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">AUX 1</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">AUX 2</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">AUX 3</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">AUX 4</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">C4-15</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Inpu</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Front - Terminal</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">D5</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Arduino UNO R4 Minima</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">5V</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">DMB1-3; AMB1-2</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">D0</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">D1</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">DMB1</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">DMB2</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">AMB1</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">AMB2</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">DMB1; AMB1</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">DMB2; AMB2</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">A5</x:t>
@@ -434,7 +374,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="5">
+  <x:fonts count="8">
     <x:font>
       <x:sz val="11"/>
       <x:color theme="1"/>
@@ -460,8 +400,23 @@
       <x:color theme="1"/>
       <x:name val="Calibri"/>
     </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:name val="Calibri"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color theme="1"/>
+      <x:name val="Calibri"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="12"/>
+      <x:color theme="1"/>
+      <x:name val="Arial"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="5">
+  <x:fills count="7">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -483,6 +438,16 @@
         <x:fgColor rgb="FFFFFF00"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFF0000"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="1">
     <x:border/>
@@ -490,7 +455,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="11">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment horizontal="center"/>
@@ -513,6 +478,70 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -762,308 +791,310 @@
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" ht="15.75" customHeight="1">
-      <x:c r="A2" s="6" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="B2" s="6"/>
-      <x:c r="C2" s="6"/>
-      <x:c r="D2" s="6"/>
-      <x:c r="E2" s="6"/>
+    <x:row r="2" ht="32" customHeight="1">
+      <x:c r="A2" s="18" t="str">
+        <x:v>Highland Technologies T660-2: master clock, pump/process trains and frames</x:v>
+      </x:c>
+      <x:c r="B2" s="18"/>
+      <x:c r="C2" s="18"/>
+      <x:c r="D2" s="18"/>
+      <x:c r="E2" s="18"/>
+      <x:c r="F2" s="9"/>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="B3" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C3" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D3" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="E3" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F3">
+      <x:c r="A3" t="str">
+        <x:v>CLOCK OUT</x:v>
+      </x:c>
+      <x:c r="B3" t="str">
+        <x:v>Output</x:v>
+      </x:c>
+      <x:c r="C3" t="str">
+        <x:v>10 MHz reference</x:v>
+      </x:c>
+      <x:c r="D3" t="str">
+        <x:v>T660-1; HF2LI</x:v>
+      </x:c>
+      <x:c r="E3" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="F3" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="2" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="B4" s="2" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C4" s="2" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D4" s="2" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E4" s="2" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F4" s="2">
+      <x:c r="A4" s="2" t="str">
+        <x:v>TRIG IN</x:v>
+      </x:c>
+      <x:c r="B4" s="2" t="str">
+        <x:v>Input</x:v>
+      </x:c>
+      <x:c r="C4" s="2" t="str">
+        <x:v>CH C</x:v>
+      </x:c>
+      <x:c r="D4" s="2" t="str">
+        <x:v>T660-1</x:v>
+      </x:c>
+      <x:c r="E4" s="2" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="F4" s="2" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="2" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="B5" s="2" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C5" s="2" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D5" s="2" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E5" s="2" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F5" s="2">
+      <x:c r="A5" s="2" t="str">
+        <x:v>CH A</x:v>
+      </x:c>
+      <x:c r="B5" s="2" t="str">
+        <x:v>Output</x:v>
+      </x:c>
+      <x:c r="C5" s="2" t="str">
+        <x:v>EXT DB9 pin 7: Fire</x:v>
+      </x:c>
+      <x:c r="D5" s="2" t="str">
+        <x:v>YAG</x:v>
+      </x:c>
+      <x:c r="E5" s="2" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="F5" s="2" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="B6" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C6" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="D6" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E6" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F6">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7">
-      <x:c r="A7" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="B7" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C7" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D7" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="E7" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F7">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="15.75" customHeight="1">
-      <x:c r="A8" s="6" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="B8" s="6"/>
-      <x:c r="C8" s="6"/>
-      <x:c r="D8" s="6"/>
-      <x:c r="E8" s="6"/>
-    </x:row>
-    <x:row r="9">
-      <x:c r="A9" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="B9" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C9" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D9" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="E9" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F9">
+      <x:c r="A6" t="str">
+        <x:v>CH B</x:v>
+      </x:c>
+      <x:c r="B6" t="str">
+        <x:v>Output</x:v>
+      </x:c>
+      <x:c r="C6" t="str">
+        <x:v>EXT DB9 pin 6: Q-switch</x:v>
+      </x:c>
+      <x:c r="D6" t="str">
+        <x:v>YAG</x:v>
+      </x:c>
+      <x:c r="E6" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="F6" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="32" customHeight="1">
+      <x:c r="A7" s="21" t="str">
+        <x:v>CH C</x:v>
+      </x:c>
+      <x:c r="B7" s="21" t="str">
+        <x:v>Output</x:v>
+      </x:c>
+      <x:c r="C7" s="21" t="str">
+        <x:v>DB9 pin 4: Process Trigger</x:v>
+      </x:c>
+      <x:c r="D7" s="21" t="str">
+        <x:v>MIRcat</x:v>
+      </x:c>
+      <x:c r="E7" s="21" t="str">
+        <x:v>Back BNC</x:v>
+      </x:c>
+      <x:c r="F7" s="21" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="32" customHeight="1">
+      <x:c r="A8" s="24" t="str">
+        <x:v>CH D</x:v>
+      </x:c>
+      <x:c r="B8" s="24" t="str">
+        <x:v>Output</x:v>
+      </x:c>
+      <x:c r="C8" s="24" t="str">
+        <x:v>SPARE / DISCONNECTED</x:v>
+      </x:c>
+      <x:c r="D8" s="24" t="str">
+        <x:v>UNASSIGNED</x:v>
+      </x:c>
+      <x:c r="E8" s="24" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="F8" s="25" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="32" customHeight="1">
+      <x:c r="A9" s="19" t="str">
+        <x:v>Highland Technologies T660-1: probe, reference and frame-trigger pulses</x:v>
+      </x:c>
+      <x:c r="B9" s="19"/>
+      <x:c r="C9" s="19"/>
+      <x:c r="D9" s="19"/>
+      <x:c r="E9" s="19"/>
+      <x:c r="F9" s="19"/>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" t="str">
+        <x:v>CLOCK IN</x:v>
+      </x:c>
+      <x:c r="B10" t="str">
+        <x:v>Input</x:v>
+      </x:c>
+      <x:c r="C10" t="str">
+        <x:v>10 MHz reference</x:v>
+      </x:c>
+      <x:c r="D10" t="str">
+        <x:v>T660-2</x:v>
+      </x:c>
+      <x:c r="E10" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="F10" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
-    <x:row r="10">
-      <x:c r="A10" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="B10" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C10" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="D10" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="E10" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F10">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
     <x:row r="11">
-      <x:c r="A11" s="2" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="B11" s="2" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C11" s="2" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="D11" s="2" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="E11" s="2" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F11" s="2">
+      <x:c r="A11" s="2" t="str">
+        <x:v>CH A</x:v>
+      </x:c>
+      <x:c r="B11" s="2" t="str">
+        <x:v>Output</x:v>
+      </x:c>
+      <x:c r="C11" s="2" t="str">
+        <x:v>DIO 0 (Ext Ref)</x:v>
+      </x:c>
+      <x:c r="D11" s="2" t="str">
+        <x:v>HF2LI</x:v>
+      </x:c>
+      <x:c r="E11" s="2" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="F11" s="2" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="2" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="B12" s="2" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C12" s="2" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="D12" s="2" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="E12" s="2" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F12" s="2">
+      <x:c r="A12" s="2" t="str">
+        <x:v>CH B</x:v>
+      </x:c>
+      <x:c r="B12" s="2" t="str">
+        <x:v>Output</x:v>
+      </x:c>
+      <x:c r="C12" s="2" t="str">
+        <x:v>TRIG IN</x:v>
+      </x:c>
+      <x:c r="D12" s="2" t="str">
+        <x:v>MIRcat</x:v>
+      </x:c>
+      <x:c r="E12" s="2" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="F12" s="2" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
-      <x:c r="A13" s="3" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="B13" s="3" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C13" s="3" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D13" s="3" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E13" s="3" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="F13" s="3">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14">
-      <x:c r="A14" s="3" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="B14" s="3" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C14" s="3" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="D14" s="3" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E14" s="3" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="F14" s="3">
-        <x:v>1</x:v>
+      <x:c r="A13" s="17" t="str">
+        <x:v>CH C</x:v>
+      </x:c>
+      <x:c r="B13" s="17" t="str">
+        <x:v>Output</x:v>
+      </x:c>
+      <x:c r="C13" s="17" t="str">
+        <x:v>TRIG IN</x:v>
+      </x:c>
+      <x:c r="D13" s="17" t="str">
+        <x:v>T660-2</x:v>
+      </x:c>
+      <x:c r="E13" s="17" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="F13" s="17" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="32" customHeight="1">
+      <x:c r="A14" s="27" t="str">
+        <x:v>CH D</x:v>
+      </x:c>
+      <x:c r="B14" s="27" t="str">
+        <x:v>Output</x:v>
+      </x:c>
+      <x:c r="C14" s="27" t="str">
+        <x:v>SPARE / DISCONNECTED</x:v>
+      </x:c>
+      <x:c r="D14" s="27" t="str">
+        <x:v>UNASSIGNED</x:v>
+      </x:c>
+      <x:c r="E14" s="27" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="F14" s="27" t="n">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="15.75" customHeight="1">
       <x:c r="A15" s="6" t="s">
-        <x:v>31</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="B15" s="6"/>
       <x:c r="C15" s="6"/>
       <x:c r="D15" s="6"/>
       <x:c r="E15" s="6"/>
     </x:row>
-    <x:row r="16">
-      <x:c r="A16" s="2" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="B16" s="2" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C16" s="2" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D16" s="2" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="E16" s="2" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F16" s="2">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17">
-      <x:c r="A17" s="2" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="B17" s="2" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C17" s="2" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D17" s="2" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="E17" s="2" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F17" s="2">
+    <x:row r="16" ht="32" customHeight="1">
+      <x:c r="A16" s="28" t="str">
+        <x:v>EXT DB9 pin 7: Fire</x:v>
+      </x:c>
+      <x:c r="B16" s="28" t="str">
+        <x:v>Input</x:v>
+      </x:c>
+      <x:c r="C16" s="28" t="str">
+        <x:v>CH A</x:v>
+      </x:c>
+      <x:c r="D16" s="28" t="str">
+        <x:v>T660-2</x:v>
+      </x:c>
+      <x:c r="E16" s="28" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="F16" s="28">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="32" customHeight="1">
+      <x:c r="A17" s="28" t="str">
+        <x:v>EXT DB9 pin 6: Q-switch</x:v>
+      </x:c>
+      <x:c r="B17" s="28" t="str">
+        <x:v>Input</x:v>
+      </x:c>
+      <x:c r="C17" s="28" t="str">
+        <x:v>CH B</x:v>
+      </x:c>
+      <x:c r="D17" s="28" t="str">
+        <x:v>T660-2</x:v>
+      </x:c>
+      <x:c r="E17" s="28" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="F17" s="28">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="3" t="s">
-        <x:v>32</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B18" s="3" t="s">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C18" s="3" t="s">
-        <x:v>33</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D18" s="3" t="s">
-        <x:v>13</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="E18" s="3" t="s">
-        <x:v>29</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="F18" s="3">
         <x:v>1</x:v>
@@ -1071,19 +1102,19 @@
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="3" t="s">
-        <x:v>34</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B19" s="3" t="s">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C19" s="3" t="s">
-        <x:v>35</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D19" s="3" t="s">
-        <x:v>13</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="E19" s="3" t="s">
-        <x:v>29</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="F19" s="3">
         <x:v>1</x:v>
@@ -1091,19 +1122,19 @@
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="3" t="s">
-        <x:v>36</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B20" s="3" t="s">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C20" s="3" t="s">
-        <x:v>37</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D20" s="3" t="s">
-        <x:v>13</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="E20" s="3" t="s">
-        <x:v>29</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="F20" s="3">
         <x:v>1</x:v>
@@ -1111,7 +1142,7 @@
     </x:row>
     <x:row r="21" ht="15.75" customHeight="1">
       <x:c r="A21" s="6" t="s">
-        <x:v>38</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B21" s="6"/>
       <x:c r="C21" s="6"/>
@@ -1120,19 +1151,19 @@
     </x:row>
     <x:row r="22">
       <x:c r="A22" t="s">
-        <x:v>15</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B22" t="s">
-        <x:v>23</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C22" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D22" t="s">
-        <x:v>24</x:v>
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="D22" t="str">
+        <x:v>T660-1</x:v>
       </x:c>
       <x:c r="E22" t="s">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F22">
         <x:v>1</x:v>
@@ -1140,19 +1171,19 @@
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="3" t="s">
-        <x:v>39</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B23" s="3" t="s">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C23" s="3" t="s">
-        <x:v>40</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D23" s="3" t="s">
-        <x:v>13</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="E23" s="3" t="s">
-        <x:v>29</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="F23" s="3">
         <x:v>1</x:v>
@@ -1160,59 +1191,59 @@
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="4" t="s">
-        <x:v>41</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B24" s="4" t="s">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C24" s="4" t="s">
-        <x:v>42</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D24" s="4" t="s">
-        <x:v>13</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="E24" s="4" t="s">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F24" s="4">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="25">
-      <x:c r="A25" s="4" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="B25" s="4" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C25" s="4" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="D25" s="4" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E25" s="4" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F25" s="4">
-        <x:v>1</x:v>
+    <x:row r="25" ht="32" customHeight="1">
+      <x:c r="A25" s="30" t="str">
+        <x:v>DB9 pin 2: Tuned / Sweep Active</x:v>
+      </x:c>
+      <x:c r="B25" s="30" t="str">
+        <x:v>Output</x:v>
+      </x:c>
+      <x:c r="C25" s="30" t="str">
+        <x:v>DIO 21; EXT</x:v>
+      </x:c>
+      <x:c r="D25" s="30" t="str">
+        <x:v>HF2LI; PicoScope</x:v>
+      </x:c>
+      <x:c r="E25" s="30" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="F25" s="30" t="n">
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="4" t="s">
-        <x:v>45</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B26" s="4" t="s">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C26" s="4" t="s">
-        <x:v>46</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D26" s="4" t="s">
-        <x:v>13</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="E26" s="4" t="s">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F26" s="4">
         <x:v>1</x:v>
@@ -1220,59 +1251,59 @@
     </x:row>
     <x:row r="27">
       <x:c r="A27" s="3" t="s">
-        <x:v>47</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B27" s="3" t="s">
-        <x:v>23</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C27" s="3" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D27" s="3" t="s">
-        <x:v>21</x:v>
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="D27" s="3" t="str">
+        <x:v>T660-2</x:v>
       </x:c>
       <x:c r="E27" s="3" t="s">
-        <x:v>48</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F27" s="3">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="28">
-      <x:c r="A28" s="3" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="B28" s="3" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C28" s="3" t="s">
+    <x:row r="28" ht="32" customHeight="1">
+      <x:c r="A28" s="32" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="D28" s="3" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="E28" s="3" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="F28" s="3">
-        <x:v>1</x:v>
+      <x:c r="B28" s="32" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C28" s="32" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="D28" s="32" t="str">
+        <x:v>UNASSIGNED</x:v>
+      </x:c>
+      <x:c r="E28" s="32" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="F28" s="32" t="n">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
       <x:c r="A29" s="2" t="s">
-        <x:v>50</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B29" s="2" t="s">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C29" s="2" t="s">
-        <x:v>51</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D29" s="2" t="s">
-        <x:v>51</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E29" s="2" t="s">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F29" s="2">
         <x:v>1</x:v>
@@ -1280,19 +1311,19 @@
     </x:row>
     <x:row r="30">
       <x:c r="A30" s="2" t="s">
-        <x:v>52</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B30" s="2" t="s">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C30" s="2" t="s">
-        <x:v>53</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D30" s="2" t="s">
-        <x:v>53</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E30" s="2" t="s">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F30" s="2">
         <x:v>1</x:v>
@@ -1300,19 +1331,19 @@
     </x:row>
     <x:row r="31">
       <x:c r="A31" s="2" t="s">
-        <x:v>54</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B31" s="2" t="s">
-        <x:v>23</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C31" s="2" t="s">
-        <x:v>51</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D31" s="2" t="s">
-        <x:v>51</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E31" s="2" t="s">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F31" s="2">
         <x:v>1</x:v>
@@ -1320,19 +1351,19 @@
     </x:row>
     <x:row r="32">
       <x:c r="A32" s="2" t="s">
-        <x:v>55</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B32" s="2" t="s">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C32" s="2" t="s">
-        <x:v>53</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D32" s="2" t="s">
-        <x:v>53</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E32" s="2" t="s">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F32" s="2">
         <x:v>1</x:v>
@@ -1340,7 +1371,7 @@
     </x:row>
     <x:row r="33" ht="15.75" customHeight="1">
       <x:c r="A33" s="6" t="s">
-        <x:v>56</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B33" s="6"/>
       <x:c r="C33" s="6"/>
@@ -1349,19 +1380,19 @@
     </x:row>
     <x:row r="34">
       <x:c r="A34" t="s">
-        <x:v>7</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B34" t="s">
-        <x:v>23</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C34" t="s">
-        <x:v>7</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D34" t="s">
-        <x:v>24</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E34" t="s">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F34">
         <x:v>3</x:v>
@@ -1372,16 +1403,16 @@
         <x:v>Signal 1 In (+)</x:v>
       </x:c>
       <x:c r="B35" s="2" t="s">
-        <x:v>23</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C35" s="7" t="str">
         <x:v>Female-to-female BNC adapter -&gt; male-to-two-female BNC tee</x:v>
       </x:c>
       <x:c r="D35" s="2" t="s">
-        <x:v>57</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E35" s="2" t="s">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F35" s="2" t="n">
         <x:v>2</x:v>
@@ -1392,16 +1423,16 @@
         <x:v>Signal 2 In (+)</x:v>
       </x:c>
       <x:c r="B36" s="2" t="s">
-        <x:v>23</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C36" s="7" t="str">
         <x:v>Female-to-female BNC adapter -&gt; male-to-two-female BNC tee</x:v>
       </x:c>
       <x:c r="D36" s="2" t="s">
-        <x:v>58</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E36" s="2" t="s">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F36" s="2" t="n">
         <x:v>2</x:v>
@@ -1409,199 +1440,199 @@
     </x:row>
     <x:row r="37">
       <x:c r="A37" t="s">
-        <x:v>12</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B37" t="s">
-        <x:v>23</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C37" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D37" t="s">
-        <x:v>24</x:v>
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="D37" t="str">
+        <x:v>T660-1</x:v>
       </x:c>
       <x:c r="E37" t="s">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F37">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="38">
-      <x:c r="A38" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="B38" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C38" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D38" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="E38" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F38">
-        <x:v>1</x:v>
+    <x:row r="38" ht="32" customHeight="1">
+      <x:c r="A38" s="33" t="str">
+        <x:v>DIO 1 (optional DAQ window)</x:v>
+      </x:c>
+      <x:c r="B38" s="33" t="str">
+        <x:v>Input</x:v>
+      </x:c>
+      <x:c r="C38" s="33" t="str">
+        <x:v>UNCONNECTED</x:v>
+      </x:c>
+      <x:c r="D38" s="33" t="str">
+        <x:v>UNASSIGNED</x:v>
+      </x:c>
+      <x:c r="E38" s="33" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="F38" s="33" t="n">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="39">
       <x:c r="A39" s="2" t="s">
-        <x:v>59</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B39" s="2" t="s">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C39" s="2" t="s">
-        <x:v>51</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D39" s="2" t="s">
-        <x:v>51</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E39" s="2" t="s">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F39" s="2">
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="40">
-      <x:c r="A40" s="4" t="s">
-        <x:v>60</x:v>
+      <x:c r="A40" s="4" t="str">
+        <x:v>DIO 9 (inactive)</x:v>
       </x:c>
       <x:c r="B40" s="4" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C40" s="4" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="D40" s="4" t="s">
-        <x:v>62</x:v>
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C40" s="4" t="str">
+        <x:v>C0</x:v>
+      </x:c>
+      <x:c r="D40" s="4" t="str">
+        <x:v>DMB 1-3 (inactive)</x:v>
       </x:c>
       <x:c r="E40" s="4" t="s">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F40" s="4">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="41">
-      <x:c r="A41" s="4" t="s">
-        <x:v>63</x:v>
+      <x:c r="A41" s="4" t="str">
+        <x:v>DIO 10 (inactive)</x:v>
       </x:c>
       <x:c r="B41" s="4" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C41" s="4" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="D41" s="4" t="s">
-        <x:v>62</x:v>
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C41" s="4" t="str">
+        <x:v>C1</x:v>
+      </x:c>
+      <x:c r="D41" s="4" t="str">
+        <x:v>DMB 1-3 (inactive)</x:v>
       </x:c>
       <x:c r="E41" s="4" t="s">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F41" s="4">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="42">
-      <x:c r="A42" s="4" t="s">
-        <x:v>65</x:v>
+      <x:c r="A42" s="4" t="str">
+        <x:v>DIO 11 (inactive)</x:v>
       </x:c>
       <x:c r="B42" s="4" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C42" s="4" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="D42" s="4" t="s">
-        <x:v>62</x:v>
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C42" s="4" t="str">
+        <x:v>C2</x:v>
+      </x:c>
+      <x:c r="D42" s="4" t="str">
+        <x:v>DMB 1-3 (inactive)</x:v>
       </x:c>
       <x:c r="E42" s="4" t="s">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F42" s="4">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="43">
-      <x:c r="A43" s="4" t="s">
-        <x:v>67</x:v>
+      <x:c r="A43" s="4" t="str">
+        <x:v>DIO 12 (inactive)</x:v>
       </x:c>
       <x:c r="B43" s="4" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C43" s="4" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="D43" s="4" t="s">
-        <x:v>62</x:v>
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C43" s="4" t="str">
+        <x:v>C3</x:v>
+      </x:c>
+      <x:c r="D43" s="4" t="str">
+        <x:v>DMB 1-3 (inactive)</x:v>
       </x:c>
       <x:c r="E43" s="4" t="s">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F43" s="4">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="44">
-      <x:c r="A44" s="4" t="s">
-        <x:v>69</x:v>
+      <x:c r="A44" s="4" t="str">
+        <x:v>DIO 13 (inactive)</x:v>
       </x:c>
       <x:c r="B44" s="4" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C44" s="4" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="D44" s="4" t="s">
-        <x:v>62</x:v>
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C44" s="4" t="str">
+        <x:v>C4</x:v>
+      </x:c>
+      <x:c r="D44" s="4" t="str">
+        <x:v>DMB 1-3 (inactive)</x:v>
       </x:c>
       <x:c r="E44" s="4" t="s">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F44" s="4">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="45">
-      <x:c r="A45" s="4" t="s">
-        <x:v>71</x:v>
+      <x:c r="A45" s="4" t="str">
+        <x:v>DIO 14 (inactive)</x:v>
       </x:c>
       <x:c r="B45" s="4" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C45" s="4" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="D45" s="4" t="s">
-        <x:v>62</x:v>
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C45" s="4" t="str">
+        <x:v>C5</x:v>
+      </x:c>
+      <x:c r="D45" s="4" t="str">
+        <x:v>DMB 1-3 (inactive)</x:v>
       </x:c>
       <x:c r="E45" s="4" t="s">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F45" s="4">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="46">
-      <x:c r="A46" s="4" t="s">
-        <x:v>73</x:v>
+      <x:c r="A46" s="4" t="str">
+        <x:v>DIO 15 (inactive)</x:v>
       </x:c>
       <x:c r="B46" s="4" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C46" s="4" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="D46" s="4" t="s">
-        <x:v>62</x:v>
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C46" s="4" t="str">
+        <x:v>C6</x:v>
+      </x:c>
+      <x:c r="D46" s="4" t="str">
+        <x:v>DMB 1-3 (inactive)</x:v>
       </x:c>
       <x:c r="E46" s="4" t="s">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F46" s="4">
         <x:v>3</x:v>
@@ -1609,19 +1640,19 @@
     </x:row>
     <x:row r="47">
       <x:c r="A47" s="3" t="s">
-        <x:v>33</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B47" s="3" t="s">
-        <x:v>23</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C47" s="3" t="s">
-        <x:v>32</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D47" s="3" t="s">
-        <x:v>26</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E47" s="3" t="s">
-        <x:v>48</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F47" s="3">
         <x:v>1</x:v>
@@ -1629,19 +1660,19 @@
     </x:row>
     <x:row r="48">
       <x:c r="A48" s="3" t="s">
-        <x:v>35</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B48" s="3" t="s">
-        <x:v>23</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C48" s="3" t="s">
-        <x:v>34</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D48" s="3" t="s">
-        <x:v>26</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E48" s="3" t="s">
-        <x:v>48</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F48" s="3">
         <x:v>1</x:v>
@@ -1649,19 +1680,19 @@
     </x:row>
     <x:row r="49">
       <x:c r="A49" s="3" t="s">
-        <x:v>37</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B49" s="3" t="s">
-        <x:v>23</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C49" s="3" t="s">
-        <x:v>36</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D49" s="3" t="s">
-        <x:v>26</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E49" s="3" t="s">
-        <x:v>48</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F49" s="3">
         <x:v>1</x:v>
@@ -1669,19 +1700,19 @@
     </x:row>
     <x:row r="50">
       <x:c r="A50" s="3" t="s">
-        <x:v>40</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B50" s="3" t="s">
-        <x:v>23</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C50" s="3" t="s">
-        <x:v>39</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D50" s="3" t="s">
-        <x:v>16</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E50" s="3" t="s">
-        <x:v>48</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F50" s="3">
         <x:v>1</x:v>
@@ -1689,59 +1720,59 @@
     </x:row>
     <x:row r="51">
       <x:c r="A51" s="4" t="s">
-        <x:v>42</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B51" s="4" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C51" s="4" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C51" s="4" t="s">
-        <x:v>41</x:v>
-      </x:c>
       <x:c r="D51" s="4" t="s">
-        <x:v>16</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E51" s="4" t="s">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F51" s="4">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="52">
-      <x:c r="A52" s="4" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="B52" s="4" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C52" s="4" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="D52" s="4" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E52" s="4" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F52" s="4">
-        <x:v>1</x:v>
+    <x:row r="52" ht="32" customHeight="1">
+      <x:c r="A52" s="30" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="B52" s="30" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C52" s="30" t="str">
+        <x:v>DB9 pin 2: Tuned / Sweep Active</x:v>
+      </x:c>
+      <x:c r="D52" s="30" t="str">
+        <x:v>MIRcat</x:v>
+      </x:c>
+      <x:c r="E52" s="30" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="F52" s="30" t="n">
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="53">
       <x:c r="A53" s="4" t="s">
-        <x:v>46</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B53" s="4" t="s">
-        <x:v>23</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C53" s="4" t="s">
-        <x:v>45</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D53" s="4" t="s">
-        <x:v>16</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E53" s="4" t="s">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F53" s="4">
         <x:v>1</x:v>
@@ -1749,19 +1780,19 @@
     </x:row>
     <x:row r="54">
       <x:c r="A54" s="2" t="s">
-        <x:v>75</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B54" s="2" t="s">
-        <x:v>23</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C54" s="2" t="s">
-        <x:v>51</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D54" s="2" t="s">
-        <x:v>51</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E54" s="2" t="s">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F54" s="2">
         <x:v>0</x:v>
@@ -1769,19 +1800,19 @@
     </x:row>
     <x:row r="55">
       <x:c r="A55" s="2" t="s">
-        <x:v>76</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B55" s="2" t="s">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C55" s="2" t="s">
-        <x:v>53</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D55" s="2" t="s">
-        <x:v>53</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E55" s="2" t="s">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F55" s="2">
         <x:v>1</x:v>
@@ -1789,19 +1820,19 @@
     </x:row>
     <x:row r="56">
       <x:c r="A56" s="2" t="s">
-        <x:v>77</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B56" s="2" t="s">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C56" s="2" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="D56" s="2" t="s">
-        <x:v>79</x:v>
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="D56" s="2" t="str">
+        <x:v>AMB1-2 (inactive)</x:v>
       </x:c>
       <x:c r="E56" s="2" t="s">
-        <x:v>29</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="F56" s="2">
         <x:v>2</x:v>
@@ -1809,19 +1840,19 @@
     </x:row>
     <x:row r="57">
       <x:c r="A57" s="2" t="s">
-        <x:v>80</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B57" s="2" t="s">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C57" s="2" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="D57" s="2" t="s">
-        <x:v>79</x:v>
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="D57" s="2" t="str">
+        <x:v>AMB1-2 (inactive)</x:v>
       </x:c>
       <x:c r="E57" s="2" t="s">
-        <x:v>29</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="F57" s="2">
         <x:v>2</x:v>
@@ -1829,19 +1860,19 @@
     </x:row>
     <x:row r="58">
       <x:c r="A58" s="2" t="s">
-        <x:v>82</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B58" s="2" t="s">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C58" s="2" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="D58" s="2" t="s">
-        <x:v>79</x:v>
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="D58" s="2" t="str">
+        <x:v>AMB1-2 (inactive)</x:v>
       </x:c>
       <x:c r="E58" s="2" t="s">
-        <x:v>29</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="F58" s="2">
         <x:v>2</x:v>
@@ -1849,19 +1880,19 @@
     </x:row>
     <x:row r="59">
       <x:c r="A59" s="2" t="s">
-        <x:v>84</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B59" s="2" t="s">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C59" s="2" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="D59" s="2" t="s">
-        <x:v>79</x:v>
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="D59" s="2" t="str">
+        <x:v>AMB1-2 (inactive)</x:v>
       </x:c>
       <x:c r="E59" s="2" t="s">
-        <x:v>29</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="F59" s="2">
         <x:v>2</x:v>
@@ -1869,7 +1900,7 @@
     </x:row>
     <x:row r="60" ht="15.75" customHeight="1">
       <x:c r="A60" s="6" t="s">
-        <x:v>86</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B60" s="6"/>
       <x:c r="C60" s="6"/>
@@ -1878,10 +1909,10 @@
     </x:row>
     <x:row r="61" ht="42" customHeight="1">
       <x:c r="A61" s="5" t="s">
-        <x:v>11</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B61" s="5" t="s">
-        <x:v>23</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C61" s="8" t="str">
         <x:v>Female-to-female BNC adapter -&gt; male-to-two-female BNC tee</x:v>
@@ -1890,7 +1921,7 @@
         <x:v>Sample Detector</x:v>
       </x:c>
       <x:c r="E61" s="5" t="s">
-        <x:v>87</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="F61" s="5" t="n">
         <x:v>2</x:v>
@@ -1898,10 +1929,10 @@
     </x:row>
     <x:row r="62" ht="42" customHeight="1">
       <x:c r="A62" s="5" t="s">
-        <x:v>14</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B62" s="5" t="s">
-        <x:v>23</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C62" s="8" t="str">
         <x:v>Female-to-female BNC adapter -&gt; male-to-two-female BNC tee</x:v>
@@ -1910,30 +1941,30 @@
         <x:v>Reference Detector</x:v>
       </x:c>
       <x:c r="E62" s="5" t="s">
-        <x:v>87</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="F62" s="5" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="63">
-      <x:c r="A63" s="5" t="str">
-        <x:v>EXT Trigger (legacy)</x:v>
-      </x:c>
-      <x:c r="B63" s="5" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C63" s="5" t="str">
-        <x:v>SIG (inactive MUX)</x:v>
-      </x:c>
-      <x:c r="D63" s="5" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="E63" s="5" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="F63" s="5">
-        <x:v>1</x:v>
+    <x:row r="63" ht="32" customHeight="1">
+      <x:c r="A63" s="34" t="str">
+        <x:v>EXT Trigger</x:v>
+      </x:c>
+      <x:c r="B63" s="34" t="str">
+        <x:v>Input</x:v>
+      </x:c>
+      <x:c r="C63" s="34" t="str">
+        <x:v>DB9 pin 2: Tuned / Sweep Active</x:v>
+      </x:c>
+      <x:c r="D63" s="34" t="str">
+        <x:v>MIRcat</x:v>
+      </x:c>
+      <x:c r="E63" s="34" t="str">
+        <x:v>Front BNC</x:v>
+      </x:c>
+      <x:c r="F63" s="34" t="n">
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="64" ht="15.75" customHeight="1">
@@ -1947,19 +1978,19 @@
     </x:row>
     <x:row r="65">
       <x:c r="A65" s="3" t="s">
-        <x:v>89</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B65" s="3" t="s">
-        <x:v>23</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C65" s="3" t="s">
-        <x:v>90</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D65" s="3" t="s">
-        <x:v>91</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E65" s="3" t="s">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F65" s="3">
         <x:v>5</x:v>
@@ -1967,39 +1998,39 @@
     </x:row>
     <x:row r="66">
       <x:c r="A66" s="5" t="s">
-        <x:v>92</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B66" s="5" t="s">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C66" s="5" t="str">
-        <x:v>CH A (legacy)</x:v>
+        <x:v>DISCONNECTED</x:v>
       </x:c>
       <x:c r="D66" s="5" t="str">
-        <x:v>PicoScope (inactive)</x:v>
+        <x:v>UNASSIGNED</x:v>
       </x:c>
       <x:c r="E66" s="5" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F66" s="5">
-        <x:v>2</x:v>
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="F66" s="5" t="n">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="67">
       <x:c r="A67" s="5" t="s">
-        <x:v>93</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B67" s="5" t="s">
-        <x:v>23</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C67" s="5" t="s">
-        <x:v>94</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D67" s="5" t="s">
-        <x:v>91</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E67" s="5" t="s">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F67" s="5">
         <x:v>1</x:v>
@@ -2007,19 +2038,19 @@
     </x:row>
     <x:row r="68">
       <x:c r="A68" s="2" t="s">
-        <x:v>76</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B68" s="2" t="s">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C68" s="2" t="s">
-        <x:v>53</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D68" s="2" t="s">
-        <x:v>53</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E68" s="2" t="s">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F68" s="2">
         <x:v>1</x:v>
@@ -2027,19 +2058,19 @@
     </x:row>
     <x:row r="69">
       <x:c r="A69" t="s">
-        <x:v>95</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B69" t="s">
-        <x:v>23</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C69" t="s">
-        <x:v>96</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D69" t="s">
-        <x:v>91</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E69" t="s">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F69">
         <x:v>2</x:v>
@@ -2047,19 +2078,19 @@
     </x:row>
     <x:row r="70">
       <x:c r="A70" t="s">
-        <x:v>97</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B70" t="s">
-        <x:v>23</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C70" t="s">
-        <x:v>98</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="D70" t="s">
-        <x:v>91</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E70" t="s">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F70">
         <x:v>2</x:v>
@@ -2067,19 +2098,19 @@
     </x:row>
     <x:row r="71">
       <x:c r="A71" t="s">
-        <x:v>99</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B71" t="s">
-        <x:v>23</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C71" t="s">
-        <x:v>100</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="D71" t="s">
-        <x:v>91</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E71" t="s">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F71">
         <x:v>2</x:v>
@@ -2087,19 +2118,19 @@
     </x:row>
     <x:row r="72">
       <x:c r="A72" t="s">
-        <x:v>101</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B72" t="s">
-        <x:v>23</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C72" t="s">
-        <x:v>102</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="D72" t="s">
-        <x:v>91</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E72" t="s">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F72">
         <x:v>2</x:v>
@@ -2107,19 +2138,19 @@
     </x:row>
     <x:row r="73">
       <x:c r="A73" s="4" t="s">
-        <x:v>78</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B73" s="4" t="s">
-        <x:v>23</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C73" s="4" t="s">
-        <x:v>60</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D73" s="4" t="s">
-        <x:v>13</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="E73" s="4" t="s">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F73" s="4">
         <x:v>3</x:v>
@@ -2127,19 +2158,19 @@
     </x:row>
     <x:row r="74">
       <x:c r="A74" s="4" t="s">
-        <x:v>81</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B74" s="4" t="s">
-        <x:v>23</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C74" s="4" t="s">
-        <x:v>63</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="D74" s="4" t="s">
-        <x:v>13</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="E74" s="4" t="s">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F74" s="4">
         <x:v>3</x:v>
@@ -2147,19 +2178,19 @@
     </x:row>
     <x:row r="75">
       <x:c r="A75" s="4" t="s">
-        <x:v>83</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B75" s="4" t="s">
-        <x:v>23</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C75" s="4" t="s">
-        <x:v>65</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="D75" s="4" t="s">
-        <x:v>13</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="E75" s="4" t="s">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F75" s="4">
         <x:v>3</x:v>
@@ -2167,19 +2198,19 @@
     </x:row>
     <x:row r="76">
       <x:c r="A76" s="4" t="s">
-        <x:v>85</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B76" s="4" t="s">
-        <x:v>23</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C76" s="4" t="s">
-        <x:v>67</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="D76" s="4" t="s">
-        <x:v>13</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="E76" s="4" t="s">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F76" s="4">
         <x:v>3</x:v>
@@ -2187,19 +2218,19 @@
     </x:row>
     <x:row r="77">
       <x:c r="A77" s="4" t="s">
-        <x:v>103</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B77" s="4" t="s">
-        <x:v>23</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C77" s="4" t="s">
-        <x:v>69</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="D77" s="4" t="s">
-        <x:v>13</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="E77" s="4" t="s">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F77" s="4">
         <x:v>3</x:v>
@@ -2207,19 +2238,19 @@
     </x:row>
     <x:row r="78">
       <x:c r="A78" s="4" t="s">
-        <x:v>104</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B78" s="4" t="s">
-        <x:v>23</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C78" s="4" t="s">
-        <x:v>71</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="D78" s="4" t="s">
-        <x:v>13</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="E78" s="4" t="s">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F78" s="4">
         <x:v>3</x:v>
@@ -2227,19 +2258,19 @@
     </x:row>
     <x:row r="79">
       <x:c r="A79" s="4" t="s">
-        <x:v>105</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B79" s="4" t="s">
-        <x:v>23</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C79" s="4" t="s">
-        <x:v>73</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="D79" s="4" t="s">
-        <x:v>13</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="E79" s="4" t="s">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F79" s="4">
         <x:v>3</x:v>
@@ -2247,19 +2278,19 @@
     </x:row>
     <x:row r="80">
       <x:c r="A80" s="2" t="s">
-        <x:v>106</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B80" s="2" t="s">
-        <x:v>23</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C80" s="2" t="s">
-        <x:v>51</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D80" s="2" t="s">
-        <x:v>51</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E80" s="2" t="s">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F80" s="2">
         <x:v>0</x:v>
@@ -2276,19 +2307,19 @@
     </x:row>
     <x:row r="82">
       <x:c r="A82" s="3" t="s">
-        <x:v>89</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B82" s="3" t="s">
-        <x:v>23</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C82" s="3" t="s">
-        <x:v>90</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D82" s="3" t="s">
-        <x:v>91</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E82" s="3" t="s">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F82" s="3">
         <x:v>5</x:v>
@@ -2296,39 +2327,39 @@
     </x:row>
     <x:row r="83">
       <x:c r="A83" s="5" t="s">
-        <x:v>92</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B83" s="5" t="s">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C83" s="5" t="str">
-        <x:v>CH B (legacy)</x:v>
+        <x:v>DISCONNECTED</x:v>
       </x:c>
       <x:c r="D83" s="5" t="str">
-        <x:v>PicoScope (inactive)</x:v>
+        <x:v>UNASSIGNED</x:v>
       </x:c>
       <x:c r="E83" s="5" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F83" s="5">
-        <x:v>2</x:v>
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="F83" s="5" t="n">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="84">
       <x:c r="A84" s="5" t="s">
-        <x:v>93</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B84" s="5" t="s">
-        <x:v>23</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C84" s="5" t="s">
-        <x:v>107</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D84" s="5" t="s">
-        <x:v>91</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E84" s="5" t="s">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F84" s="5">
         <x:v>1</x:v>
@@ -2336,19 +2367,19 @@
     </x:row>
     <x:row r="85">
       <x:c r="A85" s="2" t="s">
-        <x:v>76</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B85" s="2" t="s">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C85" s="2" t="s">
-        <x:v>53</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D85" s="2" t="s">
-        <x:v>53</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E85" s="2" t="s">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F85" s="2">
         <x:v>1</x:v>
@@ -2356,19 +2387,19 @@
     </x:row>
     <x:row r="86">
       <x:c r="A86" t="s">
-        <x:v>95</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B86" t="s">
-        <x:v>23</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C86" t="s">
-        <x:v>108</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="D86" t="s">
-        <x:v>91</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E86" t="s">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F86">
         <x:v>2</x:v>
@@ -2376,19 +2407,19 @@
     </x:row>
     <x:row r="87">
       <x:c r="A87" t="s">
-        <x:v>97</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B87" t="s">
-        <x:v>23</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C87" t="s">
-        <x:v>109</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D87" t="s">
-        <x:v>91</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E87" t="s">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F87">
         <x:v>2</x:v>
@@ -2396,19 +2427,19 @@
     </x:row>
     <x:row r="88">
       <x:c r="A88" t="s">
-        <x:v>99</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B88" t="s">
-        <x:v>23</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C88" t="s">
-        <x:v>110</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D88" t="s">
-        <x:v>91</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E88" t="s">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F88">
         <x:v>2</x:v>
@@ -2416,19 +2447,19 @@
     </x:row>
     <x:row r="89">
       <x:c r="A89" t="s">
-        <x:v>101</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B89" t="s">
-        <x:v>23</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C89" t="s">
-        <x:v>111</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D89" t="s">
-        <x:v>91</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E89" t="s">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F89">
         <x:v>2</x:v>
@@ -2436,19 +2467,19 @@
     </x:row>
     <x:row r="90">
       <x:c r="A90" s="4" t="s">
-        <x:v>78</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B90" s="4" t="s">
-        <x:v>23</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C90" s="4" t="s">
-        <x:v>60</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D90" s="4" t="s">
-        <x:v>13</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="E90" s="4" t="s">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F90" s="4">
         <x:v>3</x:v>
@@ -2456,19 +2487,19 @@
     </x:row>
     <x:row r="91">
       <x:c r="A91" s="4" t="s">
-        <x:v>81</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B91" s="4" t="s">
-        <x:v>23</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C91" s="4" t="s">
-        <x:v>63</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="D91" s="4" t="s">
-        <x:v>13</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="E91" s="4" t="s">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F91" s="4">
         <x:v>3</x:v>
@@ -2476,19 +2507,19 @@
     </x:row>
     <x:row r="92">
       <x:c r="A92" s="4" t="s">
-        <x:v>83</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B92" s="4" t="s">
-        <x:v>23</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C92" s="4" t="s">
-        <x:v>65</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="D92" s="4" t="s">
-        <x:v>13</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="E92" s="4" t="s">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F92" s="4">
         <x:v>3</x:v>
@@ -2496,19 +2527,19 @@
     </x:row>
     <x:row r="93">
       <x:c r="A93" s="4" t="s">
-        <x:v>85</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B93" s="4" t="s">
-        <x:v>23</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C93" s="4" t="s">
-        <x:v>67</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="D93" s="4" t="s">
-        <x:v>13</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="E93" s="4" t="s">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F93" s="4">
         <x:v>3</x:v>
@@ -2516,19 +2547,19 @@
     </x:row>
     <x:row r="94">
       <x:c r="A94" s="4" t="s">
-        <x:v>103</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B94" s="4" t="s">
-        <x:v>23</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C94" s="4" t="s">
-        <x:v>69</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="D94" s="4" t="s">
-        <x:v>13</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="E94" s="4" t="s">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F94" s="4">
         <x:v>3</x:v>
@@ -2536,19 +2567,19 @@
     </x:row>
     <x:row r="95">
       <x:c r="A95" s="4" t="s">
-        <x:v>104</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B95" s="4" t="s">
-        <x:v>23</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C95" s="4" t="s">
-        <x:v>71</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="D95" s="4" t="s">
-        <x:v>13</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="E95" s="4" t="s">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F95" s="4">
         <x:v>3</x:v>
@@ -2556,19 +2587,19 @@
     </x:row>
     <x:row r="96">
       <x:c r="A96" s="4" t="s">
-        <x:v>105</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B96" s="4" t="s">
-        <x:v>23</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C96" s="4" t="s">
-        <x:v>73</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="D96" s="4" t="s">
-        <x:v>13</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="E96" s="4" t="s">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F96" s="4">
         <x:v>3</x:v>
@@ -2576,19 +2607,19 @@
     </x:row>
     <x:row r="97">
       <x:c r="A97" t="s">
-        <x:v>106</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B97" t="s">
-        <x:v>23</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C97" t="s">
-        <x:v>76</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D97" t="s">
-        <x:v>112</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="E97" t="s">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F97">
         <x:v>0</x:v>
@@ -2605,19 +2636,19 @@
     </x:row>
     <x:row r="99">
       <x:c r="A99" s="3" t="s">
-        <x:v>89</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B99" s="3" t="s">
-        <x:v>23</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C99" s="3" t="s">
-        <x:v>90</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D99" s="3" t="s">
-        <x:v>91</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E99" s="3" t="s">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F99" s="3">
         <x:v>5</x:v>
@@ -2625,39 +2656,39 @@
     </x:row>
     <x:row r="100">
       <x:c r="A100" s="5" t="s">
-        <x:v>92</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B100" s="5" t="s">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C100" s="5" t="str">
-        <x:v>EXT IN (legacy)</x:v>
+        <x:v>DISCONNECTED</x:v>
       </x:c>
       <x:c r="D100" s="5" t="str">
-        <x:v>PicoScope (inactive)</x:v>
+        <x:v>UNASSIGNED</x:v>
       </x:c>
       <x:c r="E100" s="5" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F100" s="5">
-        <x:v>1</x:v>
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="F100" s="5" t="n">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="101">
       <x:c r="A101" s="5" t="s">
-        <x:v>93</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B101" s="5" t="s">
-        <x:v>23</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C101" s="5" t="s">
-        <x:v>113</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D101" s="5" t="s">
-        <x:v>91</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E101" s="5" t="s">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F101" s="5">
         <x:v>1</x:v>
@@ -2665,19 +2696,19 @@
     </x:row>
     <x:row r="102">
       <x:c r="A102" s="2" t="s">
-        <x:v>76</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B102" s="2" t="s">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C102" s="2" t="s">
-        <x:v>53</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D102" s="2" t="s">
-        <x:v>53</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E102" s="2" t="s">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F102" s="2">
         <x:v>1</x:v>
@@ -2685,19 +2716,19 @@
     </x:row>
     <x:row r="103">
       <x:c r="A103" t="s">
-        <x:v>95</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B103" t="s">
-        <x:v>23</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C103" t="s">
-        <x:v>114</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D103" t="s">
-        <x:v>91</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E103" t="s">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F103">
         <x:v>1</x:v>
@@ -2705,19 +2736,19 @@
     </x:row>
     <x:row r="104">
       <x:c r="A104" t="s">
-        <x:v>97</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B104" t="s">
-        <x:v>23</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C104" t="s">
-        <x:v>115</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D104" t="s">
-        <x:v>91</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E104" t="s">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F104">
         <x:v>1</x:v>
@@ -2725,19 +2756,19 @@
     </x:row>
     <x:row r="105">
       <x:c r="A105" t="s">
-        <x:v>99</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B105" t="s">
-        <x:v>23</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C105" t="s">
-        <x:v>116</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="D105" t="s">
-        <x:v>91</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E105" t="s">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F105">
         <x:v>1</x:v>
@@ -2745,19 +2776,19 @@
     </x:row>
     <x:row r="106">
       <x:c r="A106" t="s">
-        <x:v>101</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B106" t="s">
-        <x:v>23</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C106" t="s">
-        <x:v>117</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D106" t="s">
-        <x:v>91</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E106" t="s">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F106">
         <x:v>1</x:v>
@@ -2765,19 +2796,19 @@
     </x:row>
     <x:row r="107">
       <x:c r="A107" s="4" t="s">
-        <x:v>78</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B107" s="4" t="s">
-        <x:v>23</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C107" s="4" t="s">
-        <x:v>60</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D107" s="4" t="s">
-        <x:v>13</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="E107" s="4" t="s">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F107" s="4">
         <x:v>3</x:v>
@@ -2785,19 +2816,19 @@
     </x:row>
     <x:row r="108">
       <x:c r="A108" s="4" t="s">
-        <x:v>81</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B108" s="4" t="s">
-        <x:v>23</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C108" s="4" t="s">
-        <x:v>63</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="D108" s="4" t="s">
-        <x:v>13</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="E108" s="4" t="s">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F108" s="4">
         <x:v>3</x:v>
@@ -2805,19 +2836,19 @@
     </x:row>
     <x:row r="109">
       <x:c r="A109" s="4" t="s">
-        <x:v>83</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B109" s="4" t="s">
-        <x:v>23</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C109" s="4" t="s">
-        <x:v>65</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="D109" s="4" t="s">
-        <x:v>13</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="E109" s="4" t="s">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F109" s="4">
         <x:v>3</x:v>
@@ -2825,19 +2856,19 @@
     </x:row>
     <x:row r="110">
       <x:c r="A110" s="4" t="s">
-        <x:v>85</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B110" s="4" t="s">
-        <x:v>23</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C110" s="4" t="s">
-        <x:v>67</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="D110" s="4" t="s">
-        <x:v>13</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="E110" s="4" t="s">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F110" s="4">
         <x:v>3</x:v>
@@ -2845,19 +2876,19 @@
     </x:row>
     <x:row r="111">
       <x:c r="A111" s="4" t="s">
-        <x:v>103</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B111" s="4" t="s">
-        <x:v>23</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C111" s="4" t="s">
-        <x:v>69</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="D111" s="4" t="s">
-        <x:v>13</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="E111" s="4" t="s">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F111" s="4">
         <x:v>3</x:v>
@@ -2865,19 +2896,19 @@
     </x:row>
     <x:row r="112">
       <x:c r="A112" s="4" t="s">
-        <x:v>104</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B112" s="4" t="s">
-        <x:v>23</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C112" s="4" t="s">
-        <x:v>71</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="D112" s="4" t="s">
-        <x:v>13</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="E112" s="4" t="s">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F112" s="4">
         <x:v>3</x:v>
@@ -2885,19 +2916,19 @@
     </x:row>
     <x:row r="113">
       <x:c r="A113" s="4" t="s">
-        <x:v>105</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B113" s="4" t="s">
-        <x:v>23</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C113" s="4" t="s">
-        <x:v>73</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="D113" s="4" t="s">
-        <x:v>13</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="E113" s="4" t="s">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F113" s="4">
         <x:v>3</x:v>
@@ -2905,19 +2936,19 @@
     </x:row>
     <x:row r="114">
       <x:c r="A114" s="2" t="s">
-        <x:v>106</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B114" s="2" t="s">
-        <x:v>23</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C114" s="2" t="s">
-        <x:v>51</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D114" s="2" t="s">
-        <x:v>51</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E114" s="2" t="s">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F114" s="2">
         <x:v>0</x:v>
@@ -2934,19 +2965,19 @@
     </x:row>
     <x:row r="116">
       <x:c r="A116" s="3" t="s">
-        <x:v>89</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B116" s="3" t="s">
-        <x:v>23</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C116" s="3" t="s">
-        <x:v>90</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D116" s="3" t="s">
-        <x:v>91</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E116" s="3" t="s">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F116" s="3">
         <x:v>5</x:v>
@@ -2954,39 +2985,39 @@
     </x:row>
     <x:row r="117">
       <x:c r="A117" s="5" t="s">
-        <x:v>92</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B117" s="5" t="s">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C117" s="5" t="str">
-        <x:v>CH A (legacy)</x:v>
+        <x:v>DISCONNECTED</x:v>
       </x:c>
       <x:c r="D117" s="5" t="str">
-        <x:v>PicoScope (inactive)</x:v>
+        <x:v>UNASSIGNED</x:v>
       </x:c>
       <x:c r="E117" s="5" t="s">
-        <x:v>118</x:v>
-      </x:c>
-      <x:c r="F117" s="5">
-        <x:v>2</x:v>
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="F117" s="5" t="n">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="118">
       <x:c r="A118" s="5" t="s">
-        <x:v>93</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B118" s="5" t="s">
-        <x:v>23</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C118" s="5" t="s">
-        <x:v>119</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D118" s="5" t="s">
-        <x:v>91</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E118" s="5" t="s">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F118" s="5">
         <x:v>1</x:v>
@@ -2994,19 +3025,19 @@
     </x:row>
     <x:row r="119">
       <x:c r="A119" s="2" t="s">
-        <x:v>76</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B119" s="2" t="s">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C119" s="2" t="s">
-        <x:v>53</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D119" s="2" t="s">
-        <x:v>53</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E119" s="2" t="s">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F119" s="2">
         <x:v>1</x:v>
@@ -3014,19 +3045,19 @@
     </x:row>
     <x:row r="120">
       <x:c r="A120" t="s">
-        <x:v>95</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B120" t="s">
-        <x:v>23</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C120" t="s">
-        <x:v>96</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D120" t="s">
-        <x:v>91</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E120" t="s">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F120">
         <x:v>2</x:v>
@@ -3034,19 +3065,19 @@
     </x:row>
     <x:row r="121">
       <x:c r="A121" t="s">
-        <x:v>97</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B121" t="s">
-        <x:v>23</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C121" t="s">
-        <x:v>98</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="D121" t="s">
-        <x:v>91</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E121" t="s">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F121">
         <x:v>2</x:v>
@@ -3054,19 +3085,19 @@
     </x:row>
     <x:row r="122">
       <x:c r="A122" t="s">
-        <x:v>99</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B122" t="s">
-        <x:v>23</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C122" t="s">
-        <x:v>100</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="D122" t="s">
-        <x:v>91</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E122" t="s">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F122">
         <x:v>2</x:v>
@@ -3074,19 +3105,19 @@
     </x:row>
     <x:row r="123">
       <x:c r="A123" t="s">
-        <x:v>101</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B123" t="s">
-        <x:v>23</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C123" t="s">
-        <x:v>102</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="D123" t="s">
-        <x:v>91</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E123" t="s">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F123">
         <x:v>2</x:v>
@@ -3094,19 +3125,19 @@
     </x:row>
     <x:row r="124">
       <x:c r="A124" t="s">
-        <x:v>78</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B124" t="s">
-        <x:v>23</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C124" t="s">
-        <x:v>120</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D124" t="s">
-        <x:v>13</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="E124" t="s">
-        <x:v>48</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F124">
         <x:v>2</x:v>
@@ -3114,19 +3145,19 @@
     </x:row>
     <x:row r="125">
       <x:c r="A125" t="s">
-        <x:v>81</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B125" t="s">
-        <x:v>23</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C125" t="s">
-        <x:v>121</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D125" t="s">
-        <x:v>13</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="E125" t="s">
-        <x:v>48</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F125">
         <x:v>2</x:v>
@@ -3134,19 +3165,19 @@
     </x:row>
     <x:row r="126">
       <x:c r="A126" t="s">
-        <x:v>83</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B126" t="s">
-        <x:v>23</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C126" t="s">
-        <x:v>122</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D126" t="s">
-        <x:v>13</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="E126" t="s">
-        <x:v>48</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F126">
         <x:v>2</x:v>
@@ -3154,19 +3185,19 @@
     </x:row>
     <x:row r="127">
       <x:c r="A127" t="s">
-        <x:v>85</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B127" t="s">
-        <x:v>23</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C127" t="s">
-        <x:v>123</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="D127" t="s">
-        <x:v>13</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="E127" t="s">
-        <x:v>48</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F127">
         <x:v>2</x:v>
@@ -3174,19 +3205,19 @@
     </x:row>
     <x:row r="128">
       <x:c r="A128" s="2" t="s">
-        <x:v>124</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B128" s="2" t="s">
-        <x:v>125</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="C128" s="2" t="s">
-        <x:v>51</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D128" s="2" t="s">
-        <x:v>51</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E128" s="2" t="s">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F128" s="2">
         <x:v>0</x:v>
@@ -3203,19 +3234,19 @@
     </x:row>
     <x:row r="130">
       <x:c r="A130" s="3" t="s">
-        <x:v>89</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B130" s="3" t="s">
-        <x:v>23</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C130" s="3" t="s">
-        <x:v>90</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D130" s="3" t="s">
-        <x:v>91</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E130" s="3" t="s">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F130" s="3">
         <x:v>5</x:v>
@@ -3223,39 +3254,39 @@
     </x:row>
     <x:row r="131">
       <x:c r="A131" s="5" t="s">
-        <x:v>92</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B131" s="5" t="s">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C131" s="5" t="str">
-        <x:v>CH B (legacy)</x:v>
+        <x:v>DISCONNECTED</x:v>
       </x:c>
       <x:c r="D131" s="5" t="str">
-        <x:v>PicoScope (inactive)</x:v>
+        <x:v>UNASSIGNED</x:v>
       </x:c>
       <x:c r="E131" s="5" t="s">
-        <x:v>126</x:v>
-      </x:c>
-      <x:c r="F131" s="5">
-        <x:v>2</x:v>
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="F131" s="5" t="n">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="132">
       <x:c r="A132" s="5" t="s">
-        <x:v>93</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B132" s="5" t="s">
-        <x:v>23</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C132" s="5" t="s">
-        <x:v>127</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="D132" s="5" t="s">
-        <x:v>91</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E132" s="5" t="s">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F132" s="5">
         <x:v>1</x:v>
@@ -3263,19 +3294,19 @@
     </x:row>
     <x:row r="133">
       <x:c r="A133" s="2" t="s">
-        <x:v>76</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B133" s="2" t="s">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C133" s="2" t="s">
-        <x:v>53</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D133" s="2" t="s">
-        <x:v>53</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E133" s="2" t="s">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F133" s="2">
         <x:v>1</x:v>
@@ -3283,19 +3314,19 @@
     </x:row>
     <x:row r="134">
       <x:c r="A134" t="s">
-        <x:v>95</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B134" t="s">
-        <x:v>23</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C134" t="s">
-        <x:v>108</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="D134" t="s">
-        <x:v>91</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E134" t="s">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F134">
         <x:v>2</x:v>
@@ -3303,19 +3334,19 @@
     </x:row>
     <x:row r="135">
       <x:c r="A135" t="s">
-        <x:v>97</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B135" t="s">
-        <x:v>23</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C135" t="s">
-        <x:v>109</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D135" t="s">
-        <x:v>91</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E135" t="s">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F135">
         <x:v>2</x:v>
@@ -3323,19 +3354,19 @@
     </x:row>
     <x:row r="136">
       <x:c r="A136" t="s">
-        <x:v>99</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B136" t="s">
-        <x:v>23</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C136" t="s">
-        <x:v>110</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D136" t="s">
-        <x:v>91</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E136" t="s">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F136">
         <x:v>2</x:v>
@@ -3343,19 +3374,19 @@
     </x:row>
     <x:row r="137">
       <x:c r="A137" t="s">
-        <x:v>101</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B137" t="s">
-        <x:v>23</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C137" t="s">
-        <x:v>111</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D137" t="s">
-        <x:v>91</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E137" t="s">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F137">
         <x:v>2</x:v>
@@ -3363,19 +3394,19 @@
     </x:row>
     <x:row r="138">
       <x:c r="A138" t="s">
-        <x:v>78</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B138" t="s">
-        <x:v>23</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C138" t="s">
-        <x:v>120</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D138" t="s">
-        <x:v>13</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="E138" t="s">
-        <x:v>48</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F138">
         <x:v>2</x:v>
@@ -3383,19 +3414,19 @@
     </x:row>
     <x:row r="139">
       <x:c r="A139" t="s">
-        <x:v>81</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B139" t="s">
-        <x:v>23</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C139" t="s">
-        <x:v>121</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D139" t="s">
-        <x:v>13</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="E139" t="s">
-        <x:v>48</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F139">
         <x:v>2</x:v>
@@ -3403,19 +3434,19 @@
     </x:row>
     <x:row r="140">
       <x:c r="A140" t="s">
-        <x:v>83</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B140" t="s">
-        <x:v>23</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C140" t="s">
-        <x:v>122</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D140" t="s">
-        <x:v>13</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="E140" t="s">
-        <x:v>48</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F140">
         <x:v>2</x:v>
@@ -3423,19 +3454,19 @@
     </x:row>
     <x:row r="141">
       <x:c r="A141" t="s">
-        <x:v>85</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B141" t="s">
-        <x:v>23</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C141" t="s">
-        <x:v>123</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="D141" t="s">
-        <x:v>13</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="E141" t="s">
-        <x:v>48</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F141">
         <x:v>2</x:v>
@@ -3443,19 +3474,19 @@
     </x:row>
     <x:row r="142">
       <x:c r="A142" s="2" t="s">
-        <x:v>124</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B142" s="2" t="s">
-        <x:v>23</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C142" s="2" t="s">
-        <x:v>51</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D142" s="2" t="s">
-        <x:v>51</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E142" s="2" t="s">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F142" s="2">
         <x:v>0</x:v>
@@ -3463,7 +3494,7 @@
     </x:row>
     <x:row r="143" ht="15.75" customHeight="1">
       <x:c r="A143" s="6" t="s">
-        <x:v>128</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="B143" s="6"/>
       <x:c r="C143" s="6"/>
@@ -3472,19 +3503,19 @@
     </x:row>
     <x:row r="144">
       <x:c r="A144" s="3" t="s">
-        <x:v>129</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="B144" s="3" t="s">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C144" s="3" t="s">
-        <x:v>89</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="D144" s="3" t="s">
-        <x:v>130</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="E144" s="3" t="s">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F144" s="3">
         <x:v>5</x:v>
@@ -3492,19 +3523,19 @@
     </x:row>
     <x:row r="145">
       <x:c r="A145" s="2" t="s">
-        <x:v>76</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B145" s="2" t="s">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C145" s="2" t="s">
-        <x:v>53</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D145" s="2" t="s">
-        <x:v>53</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E145" s="2" t="s">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F145" s="2">
         <x:v>1</x:v>
@@ -3512,19 +3543,19 @@
     </x:row>
     <x:row r="146">
       <x:c r="A146" s="2" t="s">
-        <x:v>131</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="B146" s="2" t="s">
-        <x:v>23</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C146" s="2" t="s">
-        <x:v>51</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D146" s="2" t="s">
-        <x:v>51</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E146" s="2" t="s">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F146" s="2">
         <x:v>0</x:v>
@@ -3532,19 +3563,19 @@
     </x:row>
     <x:row r="147">
       <x:c r="A147" s="2" t="s">
-        <x:v>132</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="B147" s="2" t="s">
-        <x:v>23</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C147" s="2" t="s">
-        <x:v>51</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D147" s="2" t="s">
-        <x:v>51</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E147" s="2" t="s">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F147" s="2">
         <x:v>0</x:v>
@@ -3552,19 +3583,19 @@
     </x:row>
     <x:row r="148">
       <x:c r="A148" s="5" t="s">
-        <x:v>94</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B148" s="5" t="s">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C148" s="5" t="s">
-        <x:v>93</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="D148" s="5" t="s">
-        <x:v>133</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="E148" s="5" t="s">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F148" s="5">
         <x:v>1</x:v>
@@ -3572,19 +3603,19 @@
     </x:row>
     <x:row r="149">
       <x:c r="A149" s="5" t="s">
-        <x:v>107</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B149" s="5" t="s">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C149" s="5" t="s">
-        <x:v>93</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="D149" s="5" t="s">
-        <x:v>134</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="E149" s="5" t="s">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F149" s="5">
         <x:v>1</x:v>
@@ -3592,19 +3623,19 @@
     </x:row>
     <x:row r="150">
       <x:c r="A150" s="5" t="s">
-        <x:v>119</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="B150" s="5" t="s">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C150" s="5" t="s">
-        <x:v>93</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="D150" s="5" t="s">
-        <x:v>135</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="E150" s="5" t="s">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F150" s="5">
         <x:v>1</x:v>
@@ -3612,19 +3643,19 @@
     </x:row>
     <x:row r="151">
       <x:c r="A151" s="5" t="s">
-        <x:v>127</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B151" s="5" t="s">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C151" s="5" t="s">
-        <x:v>93</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="D151" s="5" t="s">
-        <x:v>136</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="E151" s="5" t="s">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F151" s="5">
         <x:v>1</x:v>
@@ -3632,19 +3663,19 @@
     </x:row>
     <x:row r="152">
       <x:c r="A152" t="s">
-        <x:v>96</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B152" t="s">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C152" t="s">
-        <x:v>95</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="D152" t="s">
-        <x:v>137</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="E152" t="s">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F152">
         <x:v>2</x:v>
@@ -3652,19 +3683,19 @@
     </x:row>
     <x:row r="153">
       <x:c r="A153" t="s">
-        <x:v>98</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B153" t="s">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C153" t="s">
-        <x:v>97</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D153" t="s">
-        <x:v>137</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="E153" t="s">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F153">
         <x:v>2</x:v>
@@ -3672,19 +3703,19 @@
     </x:row>
     <x:row r="154">
       <x:c r="A154" t="s">
-        <x:v>100</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B154" t="s">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C154" t="s">
-        <x:v>99</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="D154" t="s">
-        <x:v>137</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="E154" t="s">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F154">
         <x:v>2</x:v>
@@ -3692,19 +3723,19 @@
     </x:row>
     <x:row r="155">
       <x:c r="A155" t="s">
-        <x:v>102</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B155" t="s">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C155" t="s">
-        <x:v>101</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D155" t="s">
-        <x:v>137</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="E155" t="s">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F155">
         <x:v>2</x:v>
@@ -3712,19 +3743,19 @@
     </x:row>
     <x:row r="156">
       <x:c r="A156" t="s">
-        <x:v>108</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B156" t="s">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C156" t="s">
-        <x:v>95</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="D156" t="s">
-        <x:v>138</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="E156" t="s">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F156">
         <x:v>2</x:v>
@@ -3732,19 +3763,19 @@
     </x:row>
     <x:row r="157">
       <x:c r="A157" t="s">
-        <x:v>109</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B157" t="s">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C157" t="s">
-        <x:v>97</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D157" t="s">
-        <x:v>138</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="E157" t="s">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F157">
         <x:v>2</x:v>
@@ -3752,19 +3783,19 @@
     </x:row>
     <x:row r="158">
       <x:c r="A158" t="s">
-        <x:v>110</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B158" t="s">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C158" t="s">
-        <x:v>99</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="D158" t="s">
-        <x:v>138</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="E158" t="s">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F158">
         <x:v>2</x:v>
@@ -3772,19 +3803,19 @@
     </x:row>
     <x:row r="159">
       <x:c r="A159" t="s">
-        <x:v>111</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B159" t="s">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C159" t="s">
-        <x:v>101</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D159" t="s">
-        <x:v>138</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="E159" t="s">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F159">
         <x:v>2</x:v>
@@ -3792,19 +3823,19 @@
     </x:row>
     <x:row r="160">
       <x:c r="A160" s="5" t="s">
-        <x:v>113</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B160" s="5" t="s">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C160" s="5" t="s">
-        <x:v>93</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="D160" s="5" t="s">
-        <x:v>88</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="E160" s="5" t="s">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F160" s="5">
         <x:v>1</x:v>
@@ -3812,19 +3843,19 @@
     </x:row>
     <x:row r="161">
       <x:c r="A161" t="s">
-        <x:v>114</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B161" t="s">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C161" t="s">
-        <x:v>95</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="D161" t="s">
-        <x:v>88</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="E161" t="s">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F161">
         <x:v>1</x:v>
@@ -3832,19 +3863,19 @@
     </x:row>
     <x:row r="162">
       <x:c r="A162" t="s">
-        <x:v>115</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B162" t="s">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C162" t="s">
-        <x:v>97</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D162" t="s">
-        <x:v>88</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="E162" t="s">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F162">
         <x:v>1</x:v>
@@ -3852,19 +3883,19 @@
     </x:row>
     <x:row r="163">
       <x:c r="A163" t="s">
-        <x:v>116</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B163" t="s">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C163" t="s">
-        <x:v>99</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="D163" t="s">
-        <x:v>88</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="E163" t="s">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F163">
         <x:v>1</x:v>
@@ -3872,19 +3903,19 @@
     </x:row>
     <x:row r="164">
       <x:c r="A164" t="s">
-        <x:v>117</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B164" t="s">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C164" t="s">
-        <x:v>101</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D164" t="s">
-        <x:v>88</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="E164" t="s">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F164">
         <x:v>1</x:v>
@@ -3892,27 +3923,27 @@
     </x:row>
     <x:row r="165">
       <x:c r="A165" s="2" t="s">
-        <x:v>139</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="B165" s="2" t="s">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C165" s="2" t="s">
-        <x:v>51</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D165" s="2" t="s">
-        <x:v>51</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E165" s="2" t="s">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F165" s="2">
         <x:v>0</x:v>
       </x:c>
     </x:row>
-    <x:row r="167" ht="20" customHeight="1">
+    <x:row r="167" ht="32" customHeight="1">
       <x:c r="A167" s="10" t="str">
-        <x:v>Default detector wiring — operator report 2026-08-31</x:v>
+        <x:v>Default detector and timing wiring</x:v>
       </x:c>
       <x:c r="B167" s="10"/>
       <x:c r="C167" s="10"/>
@@ -3920,9 +3951,9 @@
       <x:c r="E167" s="10"/>
       <x:c r="F167" s="10"/>
     </x:row>
-    <x:row r="168" ht="30" customHeight="1">
+    <x:row r="168" ht="32" customHeight="1">
       <x:c r="A168" s="9" t="str">
-        <x:v>Each detector signal -&gt; its own female-to-female BNC adapter -&gt; male-to-two-female BNC tee -&gt; two separate receiver cables.</x:v>
+        <x:v>Each detector signal uses its own female-to-female BNC adapter and male-to-two-female BNC tee, then separate receiver cables.</x:v>
       </x:c>
       <x:c r="B168" s="9"/>
       <x:c r="C168" s="9"/>
@@ -3930,9 +3961,9 @@
       <x:c r="E168" s="9"/>
       <x:c r="F168" s="9"/>
     </x:row>
-    <x:row r="169" ht="30" customHeight="1">
+    <x:row r="169" ht="32" customHeight="1">
       <x:c r="A169" s="9" t="str">
-        <x:v>Sample -&gt; HF2LI Signal 1 In (+) and PicoScope CHA. Reference -&gt; HF2LI Signal 2 In (+) and PicoScope CHB.</x:v>
+        <x:v>Sample feeds HF2LI Signal 1 In (+) and PicoScope CHA. Reference feeds HF2LI Signal 2 In (+) and PicoScope CHB.</x:v>
       </x:c>
       <x:c r="B169" s="9"/>
       <x:c r="C169" s="9"/>
@@ -3940,9 +3971,9 @@
       <x:c r="E169" s="9"/>
       <x:c r="F169" s="9"/>
     </x:row>
-    <x:row r="170" ht="30" customHeight="1">
+    <x:row r="170" ht="32" customHeight="1">
       <x:c r="A170" s="9" t="str">
-        <x:v>Both receivers stay connected even when the PicoScope is not recording. MUX entries above are retained inactive legacy wiring.</x:v>
+        <x:v>Both detector receivers stay connected even when PicoScope is not recording. The MUX boards are inactive and bypassed.</x:v>
       </x:c>
       <x:c r="B170" s="9"/>
       <x:c r="C170" s="9"/>
@@ -3950,9 +3981,9 @@
       <x:c r="E170" s="9"/>
       <x:c r="F170" s="9"/>
     </x:row>
-    <x:row r="171" ht="30" customHeight="1">
+    <x:row r="171" ht="32" customHeight="1">
       <x:c r="A171" s="9" t="str">
-        <x:v>PicoScope EXT trigger is configuration-specific; this update does not select a source. Clock, T660 and MIRcat routes are unchanged.</x:v>
+        <x:v>MIRcat pin 2 feeds HF2LI logical DIO21 and PicoScope EXT. T660-1 TRIG IN is unconnected. Both T660 D outputs are spare and disabled.</x:v>
       </x:c>
       <x:c r="B171" s="9"/>
       <x:c r="C171" s="9"/>
@@ -3960,15 +3991,45 @@
       <x:c r="E171" s="9"/>
       <x:c r="F171" s="9"/>
     </x:row>
-    <x:row r="172" ht="30" customHeight="1">
+    <x:row r="172" ht="32" customHeight="1">
       <x:c r="A172" s="9" t="str">
-        <x:v>Current authority: instrument/wiring_map.yaml and instrument/default_wiring_state.md. MS-02.1 qualifies the detector branch network; earlier phase evidence is unchanged.</x:v>
+        <x:v>Wiring authority: instrument/wiring_map.yaml and instrument/default_wiring_state.md. MS-02.1 qualifies detector loading and delay.</x:v>
       </x:c>
       <x:c r="B172" s="9"/>
       <x:c r="C172" s="9"/>
       <x:c r="D172" s="9"/>
       <x:c r="E172" s="9"/>
       <x:c r="F172" s="9"/>
+    </x:row>
+    <x:row r="173" ht="32" customHeight="1">
+      <x:c r="A173" s="9" t="str">
+        <x:v>DIO numbers are logical HF2LI bits, not connector pin numbers. Pin 1 is DIO20; pin 2 is DIO21; pin 3 is DIO22.</x:v>
+      </x:c>
+      <x:c r="B173" s="9"/>
+      <x:c r="C173" s="9"/>
+      <x:c r="D173" s="9"/>
+      <x:c r="E173" s="9"/>
+      <x:c r="F173" s="9"/>
+    </x:row>
+    <x:row r="174" ht="32" customHeight="1">
+      <x:c r="A174" s="9" t="str">
+        <x:v>HF2LI DIO1 is unconnected. A future frame-relative gate may use T660-2 D after an explicit assignment and qualification.</x:v>
+      </x:c>
+      <x:c r="B174" s="9"/>
+      <x:c r="C174" s="9"/>
+      <x:c r="D174" s="9"/>
+      <x:c r="E174" s="9"/>
+      <x:c r="F174" s="9"/>
+    </x:row>
+    <x:row r="175" ht="32" customHeight="1">
+      <x:c r="A175" s="9" t="str">
+        <x:v>T660-2 CLOCK OUT feeds CLOCK-SPLITTER-01, T660-1 CLOCK IN and HF2LI Clock In. Both receivers use external 10 MHz locking.</x:v>
+      </x:c>
+      <x:c r="B175" s="9"/>
+      <x:c r="C175" s="9"/>
+      <x:c r="D175" s="9"/>
+      <x:c r="E175" s="9"/>
+      <x:c r="F175" s="9"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -3980,7 +4041,6 @@
     <x:mergeCell ref="A98:E98"/>
     <x:mergeCell ref="A115:E115"/>
     <x:mergeCell ref="A2:E2"/>
-    <x:mergeCell ref="A8:E8"/>
     <x:mergeCell ref="A15:E15"/>
     <x:mergeCell ref="A21:E21"/>
     <x:mergeCell ref="A33:E33"/>
@@ -3990,6 +4050,10 @@
     <x:mergeCell ref="A170:F170"/>
     <x:mergeCell ref="A171:F171"/>
     <x:mergeCell ref="A172:F172"/>
+    <x:mergeCell ref="A9:E9"/>
+    <x:mergeCell ref="A173:F173"/>
+    <x:mergeCell ref="A174:F174"/>
+    <x:mergeCell ref="A175:F175"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
